--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/68.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/68.xlsx
@@ -426,13 +426,13 @@
         <v>-22.60049882880854</v>
       </c>
       <c r="E2">
-        <v>-10.56510854708885</v>
+        <v>-13.6405809131321</v>
       </c>
       <c r="F2">
-        <v>-1.448630008813019</v>
+        <v>-2.031205892588661</v>
       </c>
       <c r="G2">
-        <v>-11.28365463508363</v>
+        <v>-12.47072688073672</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.19947302225209</v>
       </c>
       <c r="E3">
-        <v>-9.905817073260133</v>
+        <v>-13.9428610816181</v>
       </c>
       <c r="F3">
-        <v>-1.074733127681017</v>
+        <v>-2.111409252895112</v>
       </c>
       <c r="G3">
-        <v>-11.35382826887956</v>
+        <v>-12.56253161908625</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.6206224456784</v>
       </c>
       <c r="E4">
-        <v>-10.64409419073063</v>
+        <v>-14.4858341720858</v>
       </c>
       <c r="F4">
-        <v>-1.554936054349085</v>
+        <v>-2.100464862769325</v>
       </c>
       <c r="G4">
-        <v>-9.027623787527572</v>
+        <v>-12.56544158861527</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.91303991940356</v>
       </c>
       <c r="E5">
-        <v>-11.33539291884556</v>
+        <v>-15.85040830176512</v>
       </c>
       <c r="F5">
-        <v>-1.008051208490462</v>
+        <v>-2.336656431962145</v>
       </c>
       <c r="G5">
-        <v>-9.86792631957862</v>
+        <v>-11.47101827042422</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.10354634226598</v>
       </c>
       <c r="E6">
-        <v>-10.97110888424653</v>
+        <v>-16.2946017887035</v>
       </c>
       <c r="F6">
-        <v>-1.260201275698215</v>
+        <v>-2.151632288872847</v>
       </c>
       <c r="G6">
-        <v>-10.4198339875216</v>
+        <v>-10.8629803028629</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.23039512297127</v>
       </c>
       <c r="E7">
-        <v>-12.91649603320164</v>
+        <v>-15.67734361061398</v>
       </c>
       <c r="F7">
-        <v>-1.620227973037742</v>
+        <v>-2.28813066950615</v>
       </c>
       <c r="G7">
-        <v>-9.700998681851949</v>
+        <v>-10.99124407923642</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.3444347606673</v>
       </c>
       <c r="E8">
-        <v>-14.28439406280259</v>
+        <v>-17.40002040787186</v>
       </c>
       <c r="F8">
-        <v>-1.240406608240918</v>
+        <v>-2.154007218216673</v>
       </c>
       <c r="G8">
-        <v>-7.585629603713986</v>
+        <v>-10.66087480823593</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.48751509715587</v>
       </c>
       <c r="E9">
-        <v>-14.96846987487529</v>
+        <v>-17.48059554589034</v>
       </c>
       <c r="F9">
-        <v>-1.422961388102471</v>
+        <v>-2.15726104537487</v>
       </c>
       <c r="G9">
-        <v>-7.697890202950672</v>
+        <v>-10.33649762466153</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.71704256190556</v>
       </c>
       <c r="E10">
-        <v>-14.39340348911523</v>
+        <v>-18.10244559662363</v>
       </c>
       <c r="F10">
-        <v>-1.519174605202827</v>
+        <v>-2.06800942792764</v>
       </c>
       <c r="G10">
-        <v>-7.538262318138094</v>
+        <v>-9.862967122360793</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.06810216570858</v>
       </c>
       <c r="E11">
-        <v>-14.00179464235393</v>
+        <v>-17.98800200150179</v>
       </c>
       <c r="F11">
-        <v>-1.457448808183222</v>
+        <v>-2.030077656186048</v>
       </c>
       <c r="G11">
-        <v>-8.608664317896187</v>
+        <v>-9.650678389655027</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.58966110585656</v>
       </c>
       <c r="E12">
-        <v>-15.7905916885978</v>
+        <v>-19.47777938054518</v>
       </c>
       <c r="F12">
-        <v>-0.5426942824153674</v>
+        <v>-1.735492812035085</v>
       </c>
       <c r="G12">
-        <v>-6.293901081927919</v>
+        <v>-8.866012885936971</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.2992920001602</v>
       </c>
       <c r="E13">
-        <v>-16.17295791990945</v>
+        <v>-21.24944973809205</v>
       </c>
       <c r="F13">
-        <v>-0.8445571625673269</v>
+        <v>-1.704388444427366</v>
       </c>
       <c r="G13">
-        <v>-6.58833438109962</v>
+        <v>-8.310791361909182</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.22585711106342</v>
       </c>
       <c r="E14">
-        <v>-18.53285893715667</v>
+        <v>-21.4923072706494</v>
       </c>
       <c r="F14">
-        <v>-0.4076082682038381</v>
+        <v>-1.523535959578567</v>
       </c>
       <c r="G14">
-        <v>-5.643514615828241</v>
+        <v>-7.614533976817363</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.36581150390519</v>
       </c>
       <c r="E15">
-        <v>-18.3761284517512</v>
+        <v>-22.29307732942575</v>
       </c>
       <c r="F15">
-        <v>0.08198006113794812</v>
+        <v>-1.215715461065673</v>
       </c>
       <c r="G15">
-        <v>-5.890901752341358</v>
+        <v>-8.084803591761913</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.71703820498398</v>
       </c>
       <c r="E16">
-        <v>-18.39138488068304</v>
+        <v>-22.23677481208838</v>
       </c>
       <c r="F16">
-        <v>0.2800170277578231</v>
+        <v>-1.088875844349013</v>
       </c>
       <c r="G16">
-        <v>-4.799835327327136</v>
+        <v>-7.951385295983745</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.25076570178048</v>
       </c>
       <c r="E17">
-        <v>-18.45221134355407</v>
+        <v>-23.37389274931044</v>
       </c>
       <c r="F17">
-        <v>0.1585502020157204</v>
+        <v>-0.6667157932277038</v>
       </c>
       <c r="G17">
-        <v>-4.358423737848412</v>
+        <v>-7.518412287084624</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.92998663611256</v>
       </c>
       <c r="E18">
-        <v>-21.12492123135512</v>
+        <v>-24.19860032169134</v>
       </c>
       <c r="F18">
-        <v>1.117069034408279</v>
+        <v>-0.2499774067577174</v>
       </c>
       <c r="G18">
-        <v>-4.739834999973385</v>
+        <v>-7.274759445939804</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.70429131836547</v>
       </c>
       <c r="E19">
-        <v>-21.43951432066798</v>
+        <v>-24.72872613139927</v>
       </c>
       <c r="F19">
-        <v>0.923174733169804</v>
+        <v>0.01444492352251003</v>
       </c>
       <c r="G19">
-        <v>-5.701333293671612</v>
+        <v>-6.979399194017107</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-18.5168919622881</v>
       </c>
       <c r="E20">
-        <v>-24.1194063682452</v>
+        <v>-25.97031143550428</v>
       </c>
       <c r="F20">
-        <v>1.294361196159846</v>
+        <v>0.2684795265716316</v>
       </c>
       <c r="G20">
-        <v>-4.817295144501252</v>
+        <v>-7.329545664069203</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.31306936003593</v>
       </c>
       <c r="E21">
-        <v>-23.01409643245302</v>
+        <v>-25.50458958313343</v>
       </c>
       <c r="F21">
-        <v>1.893449755742893</v>
+        <v>0.1366059211481587</v>
       </c>
       <c r="G21">
-        <v>-5.708288749849621</v>
+        <v>-7.402447187389494</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.03328049980356</v>
       </c>
       <c r="E22">
-        <v>-24.82365653202206</v>
+        <v>-27.06528286513694</v>
       </c>
       <c r="F22">
-        <v>1.689214115847869</v>
+        <v>0.4783439229686779</v>
       </c>
       <c r="G22">
-        <v>-6.160545686514997</v>
+        <v>-6.805767701573412</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-20.63176629763042</v>
       </c>
       <c r="E23">
-        <v>-23.87698809766659</v>
+        <v>-26.42230295468386</v>
       </c>
       <c r="F23">
-        <v>1.985758048906453</v>
+        <v>0.9267996689244548</v>
       </c>
       <c r="G23">
-        <v>-5.875156797756585</v>
+        <v>-7.433629215823889</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-21.05947043166571</v>
       </c>
       <c r="E24">
-        <v>-23.94333477035297</v>
+        <v>-27.52818347820101</v>
       </c>
       <c r="F24">
-        <v>1.81709250528764</v>
+        <v>0.8591253655853464</v>
       </c>
       <c r="G24">
-        <v>-5.955563327814404</v>
+        <v>-7.80450963258844</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-21.2902674740796</v>
       </c>
       <c r="E25">
-        <v>-23.79024517804966</v>
+        <v>-26.60840512250308</v>
       </c>
       <c r="F25">
-        <v>1.724588717417019</v>
+        <v>1.056367927865937</v>
       </c>
       <c r="G25">
-        <v>-6.014332132227546</v>
+        <v>-7.537464476663129</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-21.29937790680748</v>
       </c>
       <c r="E26">
-        <v>-24.0252412797297</v>
+        <v>-27.5426428957075</v>
       </c>
       <c r="F26">
-        <v>1.812577902942383</v>
+        <v>0.8716966692902316</v>
       </c>
       <c r="G26">
-        <v>-6.162843205119251</v>
+        <v>-8.21887075446578</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-21.09410188194088</v>
       </c>
       <c r="E27">
-        <v>-24.03135019116605</v>
+        <v>-27.60144965917111</v>
       </c>
       <c r="F27">
-        <v>1.466302104489328</v>
+        <v>0.5123285240359304</v>
       </c>
       <c r="G27">
-        <v>-5.284091997175107</v>
+        <v>-8.142354115416603</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-20.68746388575549</v>
       </c>
       <c r="E28">
-        <v>-24.70654113723569</v>
+        <v>-27.10674104467716</v>
       </c>
       <c r="F28">
-        <v>1.644985923477598</v>
+        <v>0.5469219751442407</v>
       </c>
       <c r="G28">
-        <v>-6.144506093377228</v>
+        <v>-8.168338587354343</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-20.12298759277762</v>
       </c>
       <c r="E29">
-        <v>-23.76520271678725</v>
+        <v>-26.91088454384542</v>
       </c>
       <c r="F29">
-        <v>1.384152909153701</v>
+        <v>0.7610947104032472</v>
       </c>
       <c r="G29">
-        <v>-5.811276511030808</v>
+        <v>-8.073345793650496</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-19.44380811876083</v>
       </c>
       <c r="E30">
-        <v>-23.63820619171614</v>
+        <v>-27.02445414348379</v>
       </c>
       <c r="F30">
-        <v>1.58786336411535</v>
+        <v>0.8603530060762952</v>
       </c>
       <c r="G30">
-        <v>-6.890077364822031</v>
+        <v>-7.660878303821621</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-18.70872378225494</v>
       </c>
       <c r="E31">
-        <v>-22.72029356730937</v>
+        <v>-26.35302635931452</v>
       </c>
       <c r="F31">
-        <v>1.249188664950383</v>
+        <v>0.6269513782961037</v>
       </c>
       <c r="G31">
-        <v>-5.050976622481787</v>
+        <v>-8.42095638581951</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-17.96427689055997</v>
       </c>
       <c r="E32">
-        <v>-23.64452794143085</v>
+        <v>-26.22674533313662</v>
       </c>
       <c r="F32">
-        <v>1.264064486769857</v>
+        <v>0.2196174469501</v>
       </c>
       <c r="G32">
-        <v>-6.680837644557935</v>
+        <v>-7.643554219014614</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-17.26080959366242</v>
       </c>
       <c r="E33">
-        <v>-22.9326699413211</v>
+        <v>-25.1308002815923</v>
       </c>
       <c r="F33">
-        <v>0.9584615277942574</v>
+        <v>0.0753067333409953</v>
       </c>
       <c r="G33">
-        <v>-5.369692773184042</v>
+        <v>-7.120209937984468</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.62946391447135</v>
       </c>
       <c r="E34">
-        <v>-22.53135204628734</v>
+        <v>-25.05933190480325</v>
       </c>
       <c r="F34">
-        <v>0.8729425338640421</v>
+        <v>0.1275328129852957</v>
       </c>
       <c r="G34">
-        <v>-4.213276179224606</v>
+        <v>-7.382676609428966</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.10168592606456</v>
       </c>
       <c r="E35">
-        <v>-21.41223479324578</v>
+        <v>-24.66992389640967</v>
       </c>
       <c r="F35">
-        <v>1.747198177309029</v>
+        <v>-0.01521559970212907</v>
       </c>
       <c r="G35">
-        <v>-5.387046652900902</v>
+        <v>-7.558943296121921</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.68621342559781</v>
       </c>
       <c r="E36">
-        <v>-20.87571477823901</v>
+        <v>-24.28397564215795</v>
       </c>
       <c r="F36">
-        <v>1.407980069127826</v>
+        <v>0.2965794056093964</v>
       </c>
       <c r="G36">
-        <v>-4.042677146494883</v>
+        <v>-6.72842011559388</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.39311516601773</v>
       </c>
       <c r="E37">
-        <v>-21.97331272279613</v>
+        <v>-23.89382949250112</v>
       </c>
       <c r="F37">
-        <v>1.184498140996159</v>
+        <v>0.1173322967872226</v>
       </c>
       <c r="G37">
-        <v>-4.712910333102492</v>
+        <v>-6.892474199792463</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.20981522915769</v>
       </c>
       <c r="E38">
-        <v>-20.44247114145118</v>
+        <v>-23.63719181353842</v>
       </c>
       <c r="F38">
-        <v>1.359648144644086</v>
+        <v>0.2830215163277769</v>
       </c>
       <c r="G38">
-        <v>-4.616321856448716</v>
+        <v>-6.431424454174783</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-15.12931094316743</v>
       </c>
       <c r="E39">
-        <v>-18.76667763559471</v>
+        <v>-23.47236894508124</v>
       </c>
       <c r="F39">
-        <v>0.885759034320156</v>
+        <v>-0.09418386421100594</v>
       </c>
       <c r="G39">
-        <v>-5.661560399562808</v>
+        <v>-6.460881688383219</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-15.12470098098815</v>
       </c>
       <c r="E40">
-        <v>-19.64462194840978</v>
+        <v>-22.92783353108091</v>
       </c>
       <c r="F40">
-        <v>0.9275104081560567</v>
+        <v>0.2266685102827294</v>
       </c>
       <c r="G40">
-        <v>-2.833593083551182</v>
+        <v>-6.624488848934</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-15.18076773732253</v>
       </c>
       <c r="E41">
-        <v>-19.37714763114673</v>
+        <v>-22.28006249512771</v>
       </c>
       <c r="F41">
-        <v>1.392019086010685</v>
+        <v>-0.1371090346566735</v>
       </c>
       <c r="G41">
-        <v>-3.286409502412695</v>
+        <v>-6.511456892586664</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-15.26659059866841</v>
       </c>
       <c r="E42">
-        <v>-18.40518766945842</v>
+        <v>-21.7536726764761</v>
       </c>
       <c r="F42">
-        <v>0.8464761953445978</v>
+        <v>-0.3436574763403135</v>
       </c>
       <c r="G42">
-        <v>-3.765346125579057</v>
+        <v>-6.257736682456921</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-15.3682317366352</v>
       </c>
       <c r="E43">
-        <v>-18.77100232827204</v>
+        <v>-22.02942504422517</v>
       </c>
       <c r="F43">
-        <v>0.6459541265163243</v>
+        <v>-0.2720036959981562</v>
       </c>
       <c r="G43">
-        <v>-3.692686272083133</v>
+        <v>-5.947187647600047</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.45948773743558</v>
       </c>
       <c r="E44">
-        <v>-19.12564071323473</v>
+        <v>-20.97625595815731</v>
       </c>
       <c r="F44">
-        <v>0.83223821642528</v>
+        <v>0.1596983192360005</v>
       </c>
       <c r="G44">
-        <v>-3.789867336388439</v>
+        <v>-5.534842647956125</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-15.53488562794014</v>
       </c>
       <c r="E45">
-        <v>-17.81893595289942</v>
+        <v>-20.74556190678456</v>
       </c>
       <c r="F45">
-        <v>0.913643537833193</v>
+        <v>-0.02177461279749556</v>
       </c>
       <c r="G45">
-        <v>-4.057008498134389</v>
+        <v>-5.915254125328238</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-15.57893896057723</v>
       </c>
       <c r="E46">
-        <v>-16.19631578884102</v>
+        <v>-20.36320473242092</v>
       </c>
       <c r="F46">
-        <v>0.5050985333442964</v>
+        <v>-0.4111777033425011</v>
       </c>
       <c r="G46">
-        <v>-3.64418677993281</v>
+        <v>-5.45155594327914</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-15.59671895374851</v>
       </c>
       <c r="E47">
-        <v>-15.64936216972059</v>
+        <v>-19.81467520434582</v>
       </c>
       <c r="F47">
-        <v>0.9557875578180206</v>
+        <v>-0.217334760883</v>
       </c>
       <c r="G47">
-        <v>-3.176972798521007</v>
+        <v>-5.759042723512187</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.58536428724915</v>
       </c>
       <c r="E48">
-        <v>-15.79103095057654</v>
+        <v>-19.7365590277135</v>
       </c>
       <c r="F48">
-        <v>1.077965122791725</v>
+        <v>-0.3885964079421866</v>
       </c>
       <c r="G48">
-        <v>-4.381647214806399</v>
+        <v>-6.154100054350036</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.55781469801579</v>
       </c>
       <c r="E49">
-        <v>-15.11739327109153</v>
+        <v>-19.53125613010176</v>
       </c>
       <c r="F49">
-        <v>0.6134075712603317</v>
+        <v>-0.2748681904770369</v>
       </c>
       <c r="G49">
-        <v>-3.9135989759187</v>
+        <v>-6.499903088654608</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.52128324459303</v>
       </c>
       <c r="E50">
-        <v>-14.2025101957959</v>
+        <v>-18.53961542037612</v>
       </c>
       <c r="F50">
-        <v>0.5512477097216597</v>
+        <v>-0.3200415500539023</v>
       </c>
       <c r="G50">
-        <v>-3.790307638945162</v>
+        <v>-6.47209450612473</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.49083586474451</v>
       </c>
       <c r="E51">
-        <v>-14.19018821802103</v>
+        <v>-18.35388005895151</v>
       </c>
       <c r="F51">
-        <v>-0.1475009037247933</v>
+        <v>-0.4068817899915829</v>
       </c>
       <c r="G51">
-        <v>-5.446365007873563</v>
+        <v>-6.760095415313627</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.47798675713823</v>
       </c>
       <c r="E52">
-        <v>-13.37630822699247</v>
+        <v>-17.89610114999013</v>
       </c>
       <c r="F52">
-        <v>0.2596425031185665</v>
+        <v>-0.6626220015230687</v>
       </c>
       <c r="G52">
-        <v>-4.499969422925491</v>
+        <v>-6.369364967495605</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.49324692951048</v>
       </c>
       <c r="E53">
-        <v>-12.47666346673265</v>
+        <v>-17.27882032953057</v>
       </c>
       <c r="F53">
-        <v>0.6190926567457448</v>
+        <v>-0.347452227412538</v>
       </c>
       <c r="G53">
-        <v>-4.537875169350146</v>
+        <v>-7.055939006885057</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.54489842529294</v>
       </c>
       <c r="E54">
-        <v>-12.41932392884753</v>
+        <v>-16.68950283606838</v>
       </c>
       <c r="F54">
-        <v>0.517565462756429</v>
+        <v>-0.2955318153398706</v>
       </c>
       <c r="G54">
-        <v>-4.651860562812792</v>
+        <v>-6.995766531163264</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.63366018777843</v>
       </c>
       <c r="E55">
-        <v>-11.59701191921669</v>
+        <v>-16.4949777065949</v>
       </c>
       <c r="F55">
-        <v>1.192866308499239</v>
+        <v>-0.8158658292039632</v>
       </c>
       <c r="G55">
-        <v>-5.199921376839137</v>
+        <v>-7.258299413518547</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-15.76413192448494</v>
       </c>
       <c r="E56">
-        <v>-11.57921501636655</v>
+        <v>-15.81566132070426</v>
       </c>
       <c r="F56">
-        <v>0.613299055130565</v>
+        <v>-0.656088667817189</v>
       </c>
       <c r="G56">
-        <v>-5.955841413639702</v>
+        <v>-7.720269490796145</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-15.92970884546236</v>
       </c>
       <c r="E57">
-        <v>-12.50589476645216</v>
+        <v>-16.56550868926436</v>
       </c>
       <c r="F57">
-        <v>0.368744288639081</v>
+        <v>-0.6275157909924256</v>
       </c>
       <c r="G57">
-        <v>-5.388360939479992</v>
+        <v>-7.7639918657333</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.13281598040576</v>
       </c>
       <c r="E58">
-        <v>-12.97431558933157</v>
+        <v>-16.59216328727351</v>
       </c>
       <c r="F58">
-        <v>0.205412602726894</v>
+        <v>-0.6667133081254955</v>
       </c>
       <c r="G58">
-        <v>-5.697496371391597</v>
+        <v>-7.929721085974755</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.35925927064</v>
       </c>
       <c r="E59">
-        <v>-11.29530686692966</v>
+        <v>-15.65087015156514</v>
       </c>
       <c r="F59">
-        <v>0.3522440383427176</v>
+        <v>-0.492199490642918</v>
       </c>
       <c r="G59">
-        <v>-5.759453231159057</v>
+        <v>-8.296142197897908</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.60958780642034</v>
       </c>
       <c r="E60">
-        <v>-10.92328367025153</v>
+        <v>-15.24689857076289</v>
       </c>
       <c r="F60">
-        <v>0.3685529357690343</v>
+        <v>-1.197725806179077</v>
       </c>
       <c r="G60">
-        <v>-5.914164955845817</v>
+        <v>-8.644736022092085</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.86545290737206</v>
       </c>
       <c r="E61">
-        <v>-10.54751089709504</v>
+        <v>-15.35098101735518</v>
       </c>
       <c r="F61">
-        <v>0.450438710270571</v>
+        <v>-0.7463434381892091</v>
       </c>
       <c r="G61">
-        <v>-6.298489498045349</v>
+        <v>-8.252211258591778</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-17.12630916939398</v>
       </c>
       <c r="E62">
-        <v>-10.45672405018926</v>
+        <v>-15.28301767944807</v>
       </c>
       <c r="F62">
-        <v>0.1313068548724503</v>
+        <v>-0.7447256366515417</v>
       </c>
       <c r="G62">
-        <v>-6.930313735306333</v>
+        <v>-8.517978543938931</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-17.37379370315988</v>
       </c>
       <c r="E63">
-        <v>-10.543946988051</v>
+        <v>-15.03614339044591</v>
       </c>
       <c r="F63">
-        <v>0.06873777983679523</v>
+        <v>-0.8418276919751025</v>
       </c>
       <c r="G63">
-        <v>-7.020853845259861</v>
+        <v>-8.621462886951008</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.60670959446766</v>
       </c>
       <c r="E64">
-        <v>-11.37636655166696</v>
+        <v>-15.24702536803511</v>
       </c>
       <c r="F64">
-        <v>-0.1240407105101085</v>
+        <v>-0.8491123549153213</v>
       </c>
       <c r="G64">
-        <v>-6.776363436093606</v>
+        <v>-9.491563639401036</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.8091240916116</v>
       </c>
       <c r="E65">
-        <v>-9.483084024644105</v>
+        <v>-14.48574360260564</v>
       </c>
       <c r="F65">
-        <v>0.1444787249443652</v>
+        <v>-0.7773467449737862</v>
       </c>
       <c r="G65">
-        <v>-6.730667976015045</v>
+        <v>-9.068413019116933</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.98226888282169</v>
       </c>
       <c r="E66">
-        <v>-10.61490364727719</v>
+        <v>-14.23784587847775</v>
       </c>
       <c r="F66">
-        <v>0.3987005390265195</v>
+        <v>-0.9062191752969165</v>
       </c>
       <c r="G66">
-        <v>-6.759228052382338</v>
+        <v>-8.384785365257432</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.11699812945845</v>
       </c>
       <c r="E67">
-        <v>-9.707560481204325</v>
+        <v>-14.91656450579937</v>
       </c>
       <c r="F67">
-        <v>0.3878017091078864</v>
+        <v>-1.089613919704908</v>
       </c>
       <c r="G67">
-        <v>-5.509036945477506</v>
+        <v>-8.900233995176418</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.2190682374532</v>
       </c>
       <c r="E68">
-        <v>-10.77510294377253</v>
+        <v>-14.3404248716995</v>
       </c>
       <c r="F68">
-        <v>0.07752592961309518</v>
+        <v>-0.7173555492956433</v>
       </c>
       <c r="G68">
-        <v>-7.701932379054123</v>
+        <v>-9.18539445629262</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.28304086731216</v>
       </c>
       <c r="E69">
-        <v>-9.543534624172496</v>
+        <v>-15.69670736547078</v>
       </c>
       <c r="F69">
-        <v>0.2080708337224777</v>
+        <v>-1.046788981714979</v>
       </c>
       <c r="G69">
-        <v>-7.022572018394743</v>
+        <v>-9.080532926336204</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.31641294654951</v>
       </c>
       <c r="E70">
-        <v>-10.5386894297281</v>
+        <v>-14.14055614289696</v>
       </c>
       <c r="F70">
-        <v>0.4840546878435777</v>
+        <v>-1.156149217865166</v>
       </c>
       <c r="G70">
-        <v>-7.410495123595462</v>
+        <v>-8.740755084913106</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.31591725632972</v>
       </c>
       <c r="E71">
-        <v>-10.88689285312589</v>
+        <v>-13.69198362159316</v>
       </c>
       <c r="F71">
-        <v>0.1936497856071411</v>
+        <v>-0.8986329866220786</v>
       </c>
       <c r="G71">
-        <v>-6.546207689112394</v>
+        <v>-9.560701072443177</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.28995316507691</v>
       </c>
       <c r="E72">
-        <v>-11.12479170664484</v>
+        <v>-14.67026080452218</v>
       </c>
       <c r="F72">
-        <v>-0.4828439091957004</v>
+        <v>-0.6423791873008572</v>
       </c>
       <c r="G72">
-        <v>-7.172576147324659</v>
+        <v>-9.66720794353261</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.2353220251486</v>
       </c>
       <c r="E73">
-        <v>-10.52897132450764</v>
+        <v>-14.61552966766547</v>
       </c>
       <c r="F73">
-        <v>-0.03382901524303396</v>
+        <v>-0.8702605747087928</v>
       </c>
       <c r="G73">
-        <v>-6.123401365564374</v>
+        <v>-9.678808095102216</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.16145191443573</v>
       </c>
       <c r="E74">
-        <v>-10.8244995382482</v>
+        <v>-15.55319096721969</v>
       </c>
       <c r="F74">
-        <v>-0.3678217818473778</v>
+        <v>-1.117510020361584</v>
       </c>
       <c r="G74">
-        <v>-7.473600742665049</v>
+        <v>-9.431765255325182</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.06573970959277</v>
       </c>
       <c r="E75">
-        <v>-11.19380112204773</v>
+        <v>-15.22402977702416</v>
       </c>
       <c r="F75">
-        <v>0.3238268945896806</v>
+        <v>-0.9883667138977379</v>
       </c>
       <c r="G75">
-        <v>-7.388301226300188</v>
+        <v>-9.756410593088271</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.95968571876644</v>
       </c>
       <c r="E76">
-        <v>-13.37759884208466</v>
+        <v>-16.55771518549716</v>
       </c>
       <c r="F76">
-        <v>-0.0175242596537313</v>
+        <v>-0.824692083880792</v>
       </c>
       <c r="G76">
-        <v>-7.278761895496783</v>
+        <v>-8.832655829083274</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.84115354665711</v>
       </c>
       <c r="E77">
-        <v>-12.15419083264644</v>
+        <v>-16.05345601932104</v>
       </c>
       <c r="F77">
-        <v>0.4230561974036305</v>
+        <v>-1.08827113614497</v>
       </c>
       <c r="G77">
-        <v>-7.009766828248842</v>
+        <v>-8.63735350553951</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.72288220934377</v>
       </c>
       <c r="E78">
-        <v>-12.19055900740204</v>
+        <v>-16.33407196815435</v>
       </c>
       <c r="F78">
-        <v>0.2569594211008989</v>
+        <v>-1.208130100758238</v>
       </c>
       <c r="G78">
-        <v>-6.989102402992711</v>
+        <v>-9.294390857627585</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.60192408657487</v>
       </c>
       <c r="E79">
-        <v>-12.5285869497046</v>
+        <v>-16.29320249023512</v>
       </c>
       <c r="F79">
-        <v>-0.5147103748139945</v>
+        <v>-1.362420984836271</v>
       </c>
       <c r="G79">
-        <v>-7.522692822466902</v>
+        <v>-8.649049662929755</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.49256049598933</v>
       </c>
       <c r="E80">
-        <v>-12.55341657268865</v>
+        <v>-16.78997608887656</v>
       </c>
       <c r="F80">
-        <v>-0.1367081048337186</v>
+        <v>-0.8677912114810474</v>
       </c>
       <c r="G80">
-        <v>-7.064430556193288</v>
+        <v>-8.862612955668141</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.39214021036906</v>
       </c>
       <c r="E81">
-        <v>-12.36321160741848</v>
+        <v>-17.74622677423227</v>
       </c>
       <c r="F81">
-        <v>0.1367840201397606</v>
+        <v>-1.250667595259396</v>
       </c>
       <c r="G81">
-        <v>-7.147919204148168</v>
+        <v>-8.689564119239357</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.3131759017939</v>
       </c>
       <c r="E82">
-        <v>-14.54969924101597</v>
+        <v>-18.71442810249421</v>
       </c>
       <c r="F82">
-        <v>-0.006052199492360941</v>
+        <v>-1.618078359627477</v>
       </c>
       <c r="G82">
-        <v>-6.523123255067055</v>
+        <v>-9.256733402118375</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-17.25236582436346</v>
       </c>
       <c r="E83">
-        <v>-16.3186932704243</v>
+        <v>-19.06731396801593</v>
       </c>
       <c r="F83">
-        <v>-0.07339764097255795</v>
+        <v>-0.9824256628848598</v>
       </c>
       <c r="G83">
-        <v>-6.160721145428578</v>
+        <v>-8.810644011792661</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-17.21665129569586</v>
       </c>
       <c r="E84">
-        <v>-16.21969630014262</v>
+        <v>-19.82502729592735</v>
       </c>
       <c r="F84">
-        <v>-0.03525877738026591</v>
+        <v>-1.22311775217709</v>
       </c>
       <c r="G84">
-        <v>-6.676126738255552</v>
+        <v>-8.787622478112569</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-17.20411234873137</v>
       </c>
       <c r="E85">
-        <v>-17.706512057185</v>
+        <v>-20.2878011117192</v>
       </c>
       <c r="F85">
-        <v>-0.3358940170412765</v>
+        <v>-1.503472901082763</v>
       </c>
       <c r="G85">
-        <v>-6.3836532820431</v>
+        <v>-8.932564782912939</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.21809251035348</v>
       </c>
       <c r="E86">
-        <v>-18.29251017919957</v>
+        <v>-21.53631950952995</v>
       </c>
       <c r="F86">
-        <v>-0.8301750477199219</v>
+        <v>-1.615618936808566</v>
       </c>
       <c r="G86">
-        <v>-6.112407043828455</v>
+        <v>-8.537517383711709</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.25714212945857</v>
       </c>
       <c r="E87">
-        <v>-19.84950369793881</v>
+        <v>-22.62195775423281</v>
       </c>
       <c r="F87">
-        <v>-0.7940988189606006</v>
+        <v>-1.309496591471411</v>
       </c>
       <c r="G87">
-        <v>-6.870674257416363</v>
+        <v>-8.807369882254321</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.31775171562265</v>
       </c>
       <c r="E88">
-        <v>-20.31977666668736</v>
+        <v>-23.21430026833212</v>
       </c>
       <c r="F88">
-        <v>-0.8758503979428838</v>
+        <v>-1.401256505414318</v>
       </c>
       <c r="G88">
-        <v>-5.940354681606991</v>
+        <v>-9.018725041118012</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.39586778863556</v>
       </c>
       <c r="E89">
-        <v>-22.51362759902132</v>
+        <v>-24.14659985466126</v>
       </c>
       <c r="F89">
-        <v>-0.88284430392472</v>
+        <v>-1.528179787238661</v>
       </c>
       <c r="G89">
-        <v>-6.006598697847808</v>
+        <v>-7.978505285041455</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.48075740464769</v>
       </c>
       <c r="E90">
-        <v>-23.83418496134609</v>
+        <v>-26.46665482911498</v>
       </c>
       <c r="F90">
-        <v>-0.8237692825940733</v>
+        <v>-1.281968285941578</v>
       </c>
       <c r="G90">
-        <v>-6.267966268173268</v>
+        <v>-8.487346066064054</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.56815910416053</v>
       </c>
       <c r="E91">
-        <v>-25.82404172505652</v>
+        <v>-27.92086104482813</v>
       </c>
       <c r="F91">
-        <v>-0.6932492295067748</v>
+        <v>-1.51141694447561</v>
       </c>
       <c r="G91">
-        <v>-6.359913359980986</v>
+        <v>-8.734508085480503</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.64396455769091</v>
       </c>
       <c r="E92">
-        <v>-28.7016288339126</v>
+        <v>-30.17980426254834</v>
       </c>
       <c r="F92">
-        <v>-0.4571057056233169</v>
+        <v>-1.663071135110533</v>
       </c>
       <c r="G92">
-        <v>-7.081380549354356</v>
+        <v>-8.811037966711833</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.71082843945298</v>
       </c>
       <c r="E93">
-        <v>-28.68520858716078</v>
+        <v>-31.42623956231556</v>
       </c>
       <c r="F93">
-        <v>-0.8083956119655172</v>
+        <v>-1.396603565712793</v>
       </c>
       <c r="G93">
-        <v>-7.552156677766416</v>
+        <v>-9.294996687461271</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.75952140111034</v>
       </c>
       <c r="E94">
-        <v>-29.50856441005039</v>
+        <v>-33.75648586752354</v>
       </c>
       <c r="F94">
-        <v>-0.5763309691734442</v>
+        <v>-1.422826364215814</v>
       </c>
       <c r="G94">
-        <v>-6.58029306598473</v>
+        <v>-9.337050547446633</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.80032072584265</v>
       </c>
       <c r="E95">
-        <v>-31.95105347201249</v>
+        <v>-34.76310903350357</v>
       </c>
       <c r="F95">
-        <v>-0.6492728608269547</v>
+        <v>-1.586626906077986</v>
       </c>
       <c r="G95">
-        <v>-6.529171621767304</v>
+        <v>-9.67578556702486</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.82967440256633</v>
       </c>
       <c r="E96">
-        <v>-35.36463302865344</v>
+        <v>-37.19614943444867</v>
       </c>
       <c r="F96">
-        <v>-1.011763122822407</v>
+        <v>-1.42518058437457</v>
       </c>
       <c r="G96">
-        <v>-5.668648277562387</v>
+        <v>-8.543363807134062</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.85777326487895</v>
       </c>
       <c r="E97">
-        <v>-37.94368275279084</v>
+        <v>-38.87538458055096</v>
       </c>
       <c r="F97">
-        <v>-1.085649353315109</v>
+        <v>-1.593403779800288</v>
       </c>
       <c r="G97">
-        <v>-7.258888690624538</v>
+        <v>-9.151673239429604</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.88618562742109</v>
       </c>
       <c r="E98">
-        <v>-40.58731530898864</v>
+        <v>-42.10303405138498</v>
       </c>
       <c r="F98">
-        <v>-1.243685286421199</v>
+        <v>-1.548404377378011</v>
       </c>
       <c r="G98">
-        <v>-7.089650292111456</v>
+        <v>-10.12236822863593</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.92162856549098</v>
       </c>
       <c r="E99">
-        <v>-41.6388858437318</v>
+        <v>-42.79371464279786</v>
       </c>
       <c r="F99">
-        <v>-1.088554437796727</v>
+        <v>-1.685987090941578</v>
       </c>
       <c r="G99">
-        <v>-6.499853430471519</v>
+        <v>-9.367663162048274</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.97311478306506</v>
       </c>
       <c r="E100">
-        <v>-42.42076084471115</v>
+        <v>-46.82788080592395</v>
       </c>
       <c r="F100">
-        <v>-1.548949443129053</v>
+        <v>-2.235127581238023</v>
       </c>
       <c r="G100">
-        <v>-7.785960645931904</v>
+        <v>-9.153550318750369</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.03830316066659</v>
       </c>
       <c r="E101">
-        <v>-47.65907315308383</v>
+        <v>-48.06031179982245</v>
       </c>
       <c r="F101">
-        <v>-1.501020933570476</v>
+        <v>-2.012546916840602</v>
       </c>
       <c r="G101">
-        <v>-7.577932585335181</v>
+        <v>-9.722911182776386</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.14318511261796</v>
       </c>
       <c r="E102">
-        <v>-49.50933857338932</v>
+        <v>-51.02622792631664</v>
       </c>
       <c r="F102">
-        <v>-1.195225793357428</v>
+        <v>-2.171026854874592</v>
       </c>
       <c r="G102">
-        <v>-7.629474468836094</v>
+        <v>-9.801513465515301</v>
       </c>
     </row>
   </sheetData>
